--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_30.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsACH_30.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B17CD8D-06AC-4FAF-B860-C7155FAD0A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3FC4CB-5236-4AB5-B58F-C871DDD79E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9972" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PayNowNoCFCorp" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="78">
   <si>
     <t>Result</t>
   </si>
@@ -143,21 +143,9 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>985</t>
-  </si>
-  <si>
-    <t>986</t>
-  </si>
-  <si>
-    <t>988</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
     <t>12/31/2026</t>
   </si>
   <si>
@@ -170,24 +158,6 @@
     <t>Tue May 05 23:18:42 IST 2026</t>
   </si>
   <si>
-    <t>Fri Jun 05 22:50:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:52:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 22:54:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:04:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:10:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:15:23 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Jun 05 23:18:11 IST 2026</t>
   </si>
   <si>
@@ -206,33 +176,6 @@
     <t>Fri Jun 05 23:25:08 IST 2026</t>
   </si>
   <si>
-    <t>Fri Jun 05 23:27:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:28:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:29:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:31:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:33:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:34:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:36:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:37:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 23:38:39 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Jun 05 23:50:08 IST 2026</t>
   </si>
   <si>
@@ -293,10 +236,73 @@
     <t>6114</t>
   </si>
   <si>
-    <t>Thu Jul 16 20:49:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 19:35:31 IST 2026</t>
+    <t>Fri Aug 21 21:23:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 21 21:35:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 27 20:39:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 27 20:44:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 27 20:53:59 IST 2026</t>
+  </si>
+  <si>
+    <t>6115</t>
+  </si>
+  <si>
+    <t>Mon Aug 31 21:47:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 31 21:55:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 31 22:05:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 31 22:29:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 01 19:26:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 01 19:32:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 01 19:50:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 01 20:01:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 01 20:18:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 01 21:04:11 IST 2026</t>
+  </si>
+  <si>
+    <t>6431</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:10:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:12:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:15:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:30:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:34:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:36:37 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -684,10 +690,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -697,7 +703,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -778,10 +784,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -791,7 +797,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -873,10 +879,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -886,7 +892,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -965,10 +971,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -978,7 +984,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1057,10 +1063,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1070,7 +1076,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1149,10 +1155,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1162,7 +1168,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1241,10 +1247,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1254,7 +1260,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1333,10 +1339,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1346,7 +1352,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1430,10 +1436,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1443,7 +1449,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1524,10 +1530,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1537,7 +1543,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1618,10 +1624,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1631,7 +1637,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1715,10 +1721,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1728,7 +1734,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1809,10 +1815,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1822,7 +1828,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -1907,7 +1913,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
@@ -1991,10 +1997,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2004,7 +2010,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2085,20 +2091,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2182,20 +2188,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2279,19 +2285,19 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2372,10 +2378,10 @@
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2385,7 +2391,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2403,7 +2409,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>17</v>
@@ -2471,10 +2477,10 @@
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2484,7 +2490,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2502,7 +2508,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>22</v>
@@ -2567,10 +2573,10 @@
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2580,7 +2586,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2598,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>17</v>
@@ -2663,20 +2669,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2757,10 +2763,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2770,7 +2776,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2851,20 +2857,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -2948,17 +2954,17 @@
         <v>23</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -3039,20 +3045,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -3133,20 +3139,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -3227,20 +3233,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -3321,20 +3327,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -3415,17 +3421,17 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>19</v>
@@ -3509,10 +3515,10 @@
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3540,7 +3546,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>17</v>
@@ -3630,7 +3636,7 @@
         <v>17</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>17</v>
@@ -3704,10 +3710,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3717,7 +3723,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -3798,10 +3804,10 @@
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3829,7 +3835,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>22</v>
@@ -3894,10 +3900,10 @@
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -3925,7 +3931,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>22</v>
@@ -3990,10 +3996,10 @@
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4021,7 +4027,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>22</v>
@@ -4086,10 +4092,10 @@
     </row>
     <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4117,7 +4123,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>22</v>
@@ -4198,7 +4204,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -4279,10 +4285,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4292,7 +4298,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -4373,10 +4379,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4386,7 +4392,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -4467,10 +4473,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4480,7 +4486,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -4561,10 +4567,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4574,7 +4580,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -4655,10 +4661,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -4668,7 +4674,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
